--- a/docs/import/hedax-products-template.xlsx
+++ b/docs/import/hedax-products-template.xlsx
@@ -4,212 +4,318 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="products" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="راهنما" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="کالاها" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="نمونه" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="راهنما" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="101">
+  <si>
+    <t>کد کالا</t>
+  </si>
+  <si>
+    <t>شماره فنی</t>
+  </si>
+  <si>
+    <t>نام فارسی</t>
+  </si>
+  <si>
+    <t>نام انگلیسی</t>
+  </si>
+  <si>
+    <t>برند سازنده</t>
+  </si>
+  <si>
+    <t>کد دسته</t>
+  </si>
+  <si>
+    <t>برند خودرو</t>
+  </si>
+  <si>
+    <t>خودروهای سازگار</t>
+  </si>
+  <si>
+    <t>نوع قطعه</t>
+  </si>
+  <si>
+    <t>وضعیت فیزیکی</t>
+  </si>
+  <si>
+    <t>منشا</t>
+  </si>
+  <si>
+    <t>ارز پایه</t>
+  </si>
+  <si>
+    <t>قیمت پایه</t>
+  </si>
+  <si>
+    <t>موجودی فیزیکی</t>
+  </si>
+  <si>
+    <t>واحد فروش</t>
+  </si>
+  <si>
+    <t>حد هشدار موجودی</t>
+  </si>
+  <si>
+    <t>قیمت دستی ریال</t>
+  </si>
+  <si>
+    <t>قیمت دستی درهم</t>
+  </si>
+  <si>
+    <t>توضیحات فارسی</t>
+  </si>
+  <si>
+    <t>توضیحات انگلیسی</t>
+  </si>
+  <si>
+    <t>فعال</t>
+  </si>
+  <si>
+    <t>0450102805</t>
+  </si>
+  <si>
+    <t>بلبرینگ چرخ جلو</t>
+  </si>
+  <si>
+    <t>Front wheel bearing</t>
+  </si>
+  <si>
+    <t>ایساکو</t>
+  </si>
+  <si>
+    <t>BRAKE</t>
+  </si>
+  <si>
+    <t>IKCO, SAIPA</t>
+  </si>
+  <si>
+    <t>پژو ۲۰۶، سمند</t>
+  </si>
+  <si>
+    <t>GENUINE</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>DOMESTIC</t>
+  </si>
+  <si>
+    <t>IRR</t>
+  </si>
+  <si>
+    <t>200,000,000</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>عدد</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>قطر ۱۵ میلی‌متر، به همراه توپی</t>
+  </si>
+  <si>
+    <t>TEST-SAMPLE-002</t>
+  </si>
+  <si>
+    <t>نمونهٔ درهمی (فقط نمونه)</t>
+  </si>
+  <si>
+    <t>AED sample</t>
+  </si>
+  <si>
+    <t>FILTER</t>
+  </si>
+  <si>
+    <t>TOYOTA</t>
+  </si>
+  <si>
+    <t>OEM</t>
+  </si>
+  <si>
+    <t>IMPORTED</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>45.50</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>عنوان ستون</t>
+  </si>
+  <si>
+    <t>کلید انگلیسی</t>
+  </si>
+  <si>
+    <t>توضیح</t>
+  </si>
+  <si>
+    <t>نمونه</t>
+  </si>
   <si>
     <t>sku</t>
   </si>
   <si>
+    <t>کد یکتای کالا در فروشگاه؛ متن (صفرهای ابتدایی حفظ می‌شوند). کلید تشخیص کالای تکراری. اگر فایل کد کالای جدا ندارد، در پنل می‌توانید ستون شماره فنی را به‌عنوان کد کالا انتخاب کنید.</t>
+  </si>
+  <si>
+    <t>technical_number</t>
+  </si>
+  <si>
+    <t>شماره فنی (کد قطعه نزد سازنده)؛ متن. به فهرست کدهای فنی کالا اضافه می‌شود و قابل جست‌وجوست. همان شماره با برند دیگر کالای دیگری است.</t>
+  </si>
+  <si>
     <t>name_fa</t>
   </si>
   <si>
+    <t>نام فارسی قطعه (الزامی برای کالای تازه)</t>
+  </si>
+  <si>
     <t>name_en</t>
   </si>
   <si>
+    <t>نام انگلیسی (اختیاری)</t>
+  </si>
+  <si>
+    <t>manufacturer_brand</t>
+  </si>
+  <si>
+    <t>نام برند سازنده، همان‌طور که در پنل ثبت شده است (اختیاری)</t>
+  </si>
+  <si>
     <t>category_code</t>
   </si>
   <si>
+    <t>کد یا نام دسته، همان‌طور که در پنل ثبت شده است (الزامی برای کالای تازه، یا یک مقدار برای کل فایل در پنل)</t>
+  </si>
+  <si>
     <t>vehicle_brand_codes</t>
   </si>
   <si>
-    <t>manufacturer_brand</t>
+    <t>کد یا نام برندهای خودرو، جدا با ویرگول</t>
+  </si>
+  <si>
+    <t>vehicle_models</t>
+  </si>
+  <si>
+    <t>خودروهای سازگار، جدا با ویرگول؛ فقط اضافه می‌شوند و چیزی حذف نمی‌شود</t>
   </si>
   <si>
     <t>part_type</t>
   </si>
   <si>
+    <t>GENUINE / OEM / AFTERMARKET (یا: اصلی / او ای ام / افترمارکت)</t>
+  </si>
+  <si>
     <t>condition</t>
   </si>
   <si>
+    <t>NEW / USED / REFURBISHED (یا: نو / کارکرده / بازسازی شده). کالای کارکرده یا بازسازی‌شده بدون عکس واقعی منتشر نمی‌شود.</t>
+  </si>
+  <si>
     <t>origin</t>
   </si>
   <si>
+    <t>DOMESTIC / IMPORTED / UNKNOWN (یا: داخلی / وارداتی / نامشخص)</t>
+  </si>
+  <si>
     <t>base_currency</t>
   </si>
   <si>
+    <t>IRR (ریال) یا AED (درهم). اگر ستون ارز ندارید، واحد ستون قیمت را در پنل انتخاب کنید؛ تومان فقط با انتخاب صریح «تومان، تبدیل به ریال» پذیرفته می‌شود.</t>
+  </si>
+  <si>
     <t>base_price</t>
   </si>
   <si>
+    <t>قیمت پایه در همان ارز؛ ریال عدد صحیح، درهم حداکثر دو رقم اعشار. ارقام فارسی و جداکنندهٔ هزارگان مجازند.</t>
+  </si>
+  <si>
+    <t>on_hand</t>
+  </si>
+  <si>
+    <t>تعداد موجودی. در پنل انتخاب می‌کنید که این عدد جایگزین موجودی فعلی شود (شمارش انبار) یا به آن اضافه شود (کالای رسیده). عدد صحیح.</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>واحد فروش (مثل عدد، جفت، دست)</t>
+  </si>
+  <si>
+    <t>low_stock_threshold</t>
+  </si>
+  <si>
+    <t>حد هشدار موجودی (عدد صحیح)</t>
+  </si>
+  <si>
     <t>override_price_irr</t>
   </si>
   <si>
+    <t>قیمت دستی ریالی (اختیاری؛ بر تبدیل خودکار مقدم است)</t>
+  </si>
+  <si>
     <t>override_price_aed</t>
   </si>
   <si>
-    <t>on_hand</t>
-  </si>
-  <si>
-    <t>low_stock_threshold</t>
-  </si>
-  <si>
-    <t>unit</t>
+    <t>قیمت دستی درهمی برای نمایش/مرجع (اختیاری)</t>
   </si>
   <si>
     <t>description_fa</t>
   </si>
   <si>
+    <t>توضیحات و مشخصات فارسی</t>
+  </si>
+  <si>
     <t>description_en</t>
   </si>
   <si>
     <t>is_active</t>
   </si>
   <si>
-    <t>TEST-SAMPLE-001</t>
-  </si>
-  <si>
-    <t>نمونهٔ آزمایشی — این ردیف را حذف کنید</t>
-  </si>
-  <si>
-    <t>TEST SAMPLE - delete this row</t>
-  </si>
-  <si>
-    <t>BRAKE</t>
-  </si>
-  <si>
-    <t>IKCO</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>AFTERMARKET</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>DOMESTIC</t>
-  </si>
-  <si>
-    <t>IRR</t>
-  </si>
-  <si>
-    <t>12000000</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>عدد</t>
-  </si>
-  <si>
-    <t>TEST-SAMPLE-002</t>
-  </si>
-  <si>
-    <t>نمونهٔ آزمایشی درهمی — حذف کنید</t>
-  </si>
-  <si>
-    <t>TEST SAMPLE AED - delete</t>
-  </si>
-  <si>
-    <t>FILTER</t>
-  </si>
-  <si>
-    <t>TOYOTA</t>
-  </si>
-  <si>
-    <t>GENUINE</t>
-  </si>
-  <si>
-    <t>IMPORTED</t>
-  </si>
-  <si>
-    <t>AED</t>
-  </si>
-  <si>
-    <t>45.50</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>ستون</t>
-  </si>
-  <si>
-    <t>توضیح</t>
-  </si>
-  <si>
-    <t>کد کالای یکتا؛ متن (صفرهای ابتدایی حفظ می‌شوند). کلید به‌روزرسانی.</t>
-  </si>
-  <si>
-    <t>نام فارسی قطعه (الزامی در ایجاد)</t>
-  </si>
-  <si>
-    <t>نام انگلیسی (اختیاری)</t>
-  </si>
-  <si>
-    <t>کد دستهٔ ثبت‌شده در پنل (مثل BRAKE)</t>
-  </si>
-  <si>
-    <t>کد برندهای خودرو، جدا با ویرگول (مثل IKCO,SAIPA)</t>
-  </si>
-  <si>
-    <t>نام برند سازندهٔ ثبت‌شده در پنل</t>
-  </si>
-  <si>
-    <t>GENUINE / OEM / AFTERMARKET (یا: اصلی / او ای ام / افترمارکت)</t>
-  </si>
-  <si>
-    <t>NEW / USED / REFURBISHED (یا: نو / کارکرده / بازسازی شده)</t>
-  </si>
-  <si>
-    <t>DOMESTIC / IMPORTED / UNKNOWN (یا: داخلی / وارداتی / نامشخص)</t>
-  </si>
-  <si>
-    <t>IRR (ریال) یا AED (درهم). تومان پذیرفته نمی‌شود.</t>
-  </si>
-  <si>
-    <t>قیمت پایه در همان ارز؛ ریال عدد صحیح، درهم حداکثر دو رقم اعشار</t>
-  </si>
-  <si>
-    <t>قیمت دستی ریالی (اختیاری؛ بر تبدیل خودکار مقدم است)</t>
-  </si>
-  <si>
-    <t>قیمت دستی درهمی برای نمایش/مرجع (اختیاری)</t>
-  </si>
-  <si>
-    <t>موجودی فیزیکی مطلق (شمارش انبار)، نه موجودی قابل فروش. عدد صحیح ≥ رزروشده.</t>
-  </si>
-  <si>
-    <t>حد هشدار موجودی (عدد صحیح)</t>
-  </si>
-  <si>
-    <t>واحد فروش (مثل عدد، جفت، دست)</t>
-  </si>
-  <si>
-    <t>توضیحات فارسی</t>
-  </si>
-  <si>
-    <t>توضیحات انگلیسی</t>
-  </si>
-  <si>
     <t>1 یا 0 (فعال بودن فروش)</t>
   </si>
   <si>
     <t>نکته</t>
   </si>
   <si>
-    <t>سلول خالی در به‌روزرسانی یعنی «بدون تغییر». فرمول در ستون‌های قیمت و موجودی پذیرفته نمی‌شود؛ خروجی «فقط مقادیر» بگیرید. حداکثر ۵۰۰۰ ردیف.</t>
+    <t>کالاها را در شیت «کالاها» بنویسید؛ ستون‌هایی را که ندارید خالی بگذارید یا حذف کنید. ترتیب ستون‌ها مهم نیست و در پنل هم می‌توانید ستون‌ها را تطبیق دهید.</t>
+  </si>
+  <si>
+    <t>پیش از هر تغییری پیش‌نمایش نشان داده می‌شود؛ تا تأیید نکنید چیزی ثبت نمی‌شود. ردیف خطادار هرگز بی‌صدا حذف نمی‌شود.</t>
+  </si>
+  <si>
+    <t>سلول خالی در کالای موجود یعنی «بدون تغییر». با فایل هیچ کالایی حذف نمی‌شود.</t>
+  </si>
+  <si>
+    <t>کد کالا و شماره فنی را «متن» نگه دارید تا صفرهای ابتدایی حذف نشوند. اگر Excel عددی را گرد کرده باشد، پنل خطا می‌دهد و مقدار را حدس نمی‌زند.</t>
+  </si>
+  <si>
+    <t>فرمول‌ها اجرا نمی‌شوند؛ در ستون‌های کد، قیمت و موجودی فرمول پذیرفته نیست. فایل را با «فقط مقادیر» ذخیره کنید. حداکثر ۵۰۰۰ ردیف.</t>
+  </si>
+  <si>
+    <t>کالای تازه پیش‌نویس (منتشرنشده) ثبت می‌شود. پس از ثبت، از دکمهٔ «مشاهدهٔ قطعات واردشده و افزودن عکس» برای هر قطعه عکس بگذارید.</t>
   </si>
 </sst>
 </file>
@@ -592,17 +698,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="1" max="2" width="18" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="40" customWidth="1"/>
+    <col min="20" max="21" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -656,123 +766,11 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -783,179 +781,599 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
+    <col min="1" max="2" width="18" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="40" customWidth="1"/>
+    <col min="20" max="21" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" t="s">
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="110" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>92</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/docs/import/hedax-products-template.xlsx
+++ b/docs/import/hedax-products-template.xlsx
@@ -13,284 +13,293 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
   <si>
     <t>کد کالا</t>
   </si>
   <si>
+    <t>نام قطعه</t>
+  </si>
+  <si>
+    <t>کد دسته</t>
+  </si>
+  <si>
+    <t>نوع قطعه</t>
+  </si>
+  <si>
+    <t>وضعیت فیزیکی</t>
+  </si>
+  <si>
+    <t>منشا</t>
+  </si>
+  <si>
+    <t>ارز پایه</t>
+  </si>
+  <si>
+    <t>قیمت پایه</t>
+  </si>
+  <si>
+    <t>موجودی</t>
+  </si>
+  <si>
+    <t>00123</t>
+  </si>
+  <si>
+    <t>فیلتر روغن پژو ۴۰۵ (فقط نمونه)</t>
+  </si>
+  <si>
+    <t>FILTER</t>
+  </si>
+  <si>
+    <t>اصلی</t>
+  </si>
+  <si>
+    <t>نو</t>
+  </si>
+  <si>
+    <t>داخلی</t>
+  </si>
+  <si>
+    <t>ریال</t>
+  </si>
+  <si>
+    <t>1250000</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>TEST-SAMPLE-002</t>
+  </si>
+  <si>
+    <t>لنت ترمز کارکرده (فقط نمونه)</t>
+  </si>
+  <si>
+    <t>BRAKE</t>
+  </si>
+  <si>
+    <t>افترمارکت</t>
+  </si>
+  <si>
+    <t>کارکرده</t>
+  </si>
+  <si>
+    <t>وارداتی</t>
+  </si>
+  <si>
+    <t>درهم</t>
+  </si>
+  <si>
+    <t>45.50</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>عنوان ستون</t>
+  </si>
+  <si>
+    <t>کلید انگلیسی</t>
+  </si>
+  <si>
+    <t>توضیح</t>
+  </si>
+  <si>
+    <t>نمونه</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>کد یکتای کالا در فروشگاه؛ متن (صفرهای ابتدایی حفظ می‌شوند). کلید تشخیص کالای تکراری. اگر فایل کد کالای جدا ندارد، در پنل می‌توانید ستون شماره فنی را به‌عنوان کد کالا انتخاب کنید.</t>
+  </si>
+  <si>
+    <t>0450102805</t>
+  </si>
+  <si>
+    <t>name_fa</t>
+  </si>
+  <si>
+    <t>نام فارسی قطعه (الزامی برای کالای تازه)</t>
+  </si>
+  <si>
+    <t>بلبرینگ چرخ جلو</t>
+  </si>
+  <si>
+    <t>category_code</t>
+  </si>
+  <si>
+    <t>کد یا نام دسته، همان‌طور که در پنل ثبت شده است (الزامی برای کالای تازه، یا یک مقدار برای کل فایل در پنل)</t>
+  </si>
+  <si>
+    <t>part_type</t>
+  </si>
+  <si>
+    <t>اصلی / او ای ام / افترمارکت (کد انگلیسی هم پذیرفته است: GENUINE / OEM / AFTERMARKET). حدس زده نمی‌شود؛ اگر نمی‌دانید خالی بگذارید.</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>نو / کارکرده / بازسازی شده (یا NEW / USED / REFURBISHED). کالای کارکرده یا بازسازی‌شده بدون عکس واقعی منتشر نمی‌شود.</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>داخلی / وارداتی / نامشخص (یا DOMESTIC / IMPORTED / UNKNOWN)</t>
+  </si>
+  <si>
+    <t>base_currency</t>
+  </si>
+  <si>
+    <t>ریال یا درهم (یا IRR / AED). اگر ستون ارز ندارید، واحد ستون قیمت را در پنل انتخاب کنید؛ تومان فقط با انتخاب صریح «تومان، تبدیل به ریال» پذیرفته می‌شود.</t>
+  </si>
+  <si>
+    <t>base_price</t>
+  </si>
+  <si>
+    <t>قیمت پایه در همان ارز؛ ریال عدد صحیح، درهم حداکثر دو رقم اعشار. ارقام فارسی و جداکنندهٔ هزارگان مجازند.</t>
+  </si>
+  <si>
+    <t>200,000,000</t>
+  </si>
+  <si>
+    <t>on_hand</t>
+  </si>
+  <si>
+    <t>تعداد موجودی. در پنل انتخاب می‌کنید که این عدد جایگزین موجودی فعلی شود (شمارش انبار) یا به آن اضافه شود (کالای رسیده). عدد صحیح.</t>
+  </si>
+  <si>
+    <t>ستون‌های اختیاری</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>در صورت نیاز، با همین عنوان به شیت «کالاها» اضافه کنید:</t>
+  </si>
+  <si>
     <t>شماره فنی</t>
   </si>
   <si>
-    <t>نام فارسی</t>
+    <t>technical_number</t>
+  </si>
+  <si>
+    <t>شماره فنی (کد قطعه نزد سازنده)؛ متن. به فهرست کدهای فنی کالا اضافه می‌شود و قابل جست‌وجوست. همان شماره با برند دیگر کالای دیگری است.</t>
   </si>
   <si>
     <t>نام انگلیسی</t>
   </si>
   <si>
+    <t>name_en</t>
+  </si>
+  <si>
+    <t>نام انگلیسی (اختیاری)</t>
+  </si>
+  <si>
+    <t>Front wheel bearing</t>
+  </si>
+  <si>
     <t>برند سازنده</t>
   </si>
   <si>
-    <t>کد دسته</t>
+    <t>manufacturer_brand</t>
+  </si>
+  <si>
+    <t>نام برند سازنده، همان‌طور که در پنل ثبت شده است (اختیاری)</t>
+  </si>
+  <si>
+    <t>ایساکو</t>
   </si>
   <si>
     <t>برند خودرو</t>
   </si>
   <si>
+    <t>vehicle_brand_codes</t>
+  </si>
+  <si>
+    <t>کد یا نام برندهای خودرو، جدا با ویرگول</t>
+  </si>
+  <si>
+    <t>IKCO, SAIPA</t>
+  </si>
+  <si>
     <t>خودروهای سازگار</t>
   </si>
   <si>
-    <t>نوع قطعه</t>
-  </si>
-  <si>
-    <t>وضعیت فیزیکی</t>
-  </si>
-  <si>
-    <t>منشا</t>
-  </si>
-  <si>
-    <t>ارز پایه</t>
-  </si>
-  <si>
-    <t>قیمت پایه</t>
-  </si>
-  <si>
-    <t>موجودی فیزیکی</t>
+    <t>vehicle_models</t>
+  </si>
+  <si>
+    <t>خودروهای سازگار، جدا با ویرگول؛ فقط اضافه می‌شوند و چیزی حذف نمی‌شود</t>
+  </si>
+  <si>
+    <t>پژو ۲۰۶، سمند</t>
   </si>
   <si>
     <t>واحد فروش</t>
   </si>
   <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>واحد فروش (مثل عدد، جفت، دست)</t>
+  </si>
+  <si>
+    <t>عدد</t>
+  </si>
+  <si>
     <t>حد هشدار موجودی</t>
   </si>
   <si>
+    <t>low_stock_threshold</t>
+  </si>
+  <si>
+    <t>حد هشدار موجودی (عدد صحیح)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>قیمت دستی ریال</t>
   </si>
   <si>
+    <t>override_price_irr</t>
+  </si>
+  <si>
+    <t>قیمت دستی ریالی (اختیاری؛ بر تبدیل خودکار مقدم است)</t>
+  </si>
+  <si>
     <t>قیمت دستی درهم</t>
   </si>
   <si>
+    <t>override_price_aed</t>
+  </si>
+  <si>
+    <t>قیمت دستی درهمی برای نمایش/مرجع (اختیاری)</t>
+  </si>
+  <si>
     <t>توضیحات فارسی</t>
   </si>
   <si>
+    <t>description_fa</t>
+  </si>
+  <si>
+    <t>توضیحات و مشخصات فارسی</t>
+  </si>
+  <si>
+    <t>قطر ۱۵ میلی‌متر، به همراه توپی</t>
+  </si>
+  <si>
     <t>توضیحات انگلیسی</t>
   </si>
   <si>
+    <t>description_en</t>
+  </si>
+  <si>
     <t>فعال</t>
   </si>
   <si>
-    <t>0450102805</t>
-  </si>
-  <si>
-    <t>بلبرینگ چرخ جلو</t>
-  </si>
-  <si>
-    <t>Front wheel bearing</t>
-  </si>
-  <si>
-    <t>ایساکو</t>
-  </si>
-  <si>
-    <t>BRAKE</t>
-  </si>
-  <si>
-    <t>IKCO, SAIPA</t>
-  </si>
-  <si>
-    <t>پژو ۲۰۶، سمند</t>
-  </si>
-  <si>
-    <t>GENUINE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>DOMESTIC</t>
-  </si>
-  <si>
-    <t>IRR</t>
-  </si>
-  <si>
-    <t>200,000,000</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>عدد</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>قطر ۱۵ میلی‌متر، به همراه توپی</t>
-  </si>
-  <si>
-    <t>TEST-SAMPLE-002</t>
-  </si>
-  <si>
-    <t>نمونهٔ درهمی (فقط نمونه)</t>
-  </si>
-  <si>
-    <t>AED sample</t>
-  </si>
-  <si>
-    <t>FILTER</t>
-  </si>
-  <si>
-    <t>TOYOTA</t>
-  </si>
-  <si>
-    <t>OEM</t>
-  </si>
-  <si>
-    <t>IMPORTED</t>
-  </si>
-  <si>
-    <t>AED</t>
-  </si>
-  <si>
-    <t>45.50</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>عنوان ستون</t>
-  </si>
-  <si>
-    <t>کلید انگلیسی</t>
-  </si>
-  <si>
-    <t>توضیح</t>
-  </si>
-  <si>
-    <t>نمونه</t>
-  </si>
-  <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>کد یکتای کالا در فروشگاه؛ متن (صفرهای ابتدایی حفظ می‌شوند). کلید تشخیص کالای تکراری. اگر فایل کد کالای جدا ندارد، در پنل می‌توانید ستون شماره فنی را به‌عنوان کد کالا انتخاب کنید.</t>
-  </si>
-  <si>
-    <t>technical_number</t>
-  </si>
-  <si>
-    <t>شماره فنی (کد قطعه نزد سازنده)؛ متن. به فهرست کدهای فنی کالا اضافه می‌شود و قابل جست‌وجوست. همان شماره با برند دیگر کالای دیگری است.</t>
-  </si>
-  <si>
-    <t>name_fa</t>
-  </si>
-  <si>
-    <t>نام فارسی قطعه (الزامی برای کالای تازه)</t>
-  </si>
-  <si>
-    <t>name_en</t>
-  </si>
-  <si>
-    <t>نام انگلیسی (اختیاری)</t>
-  </si>
-  <si>
-    <t>manufacturer_brand</t>
-  </si>
-  <si>
-    <t>نام برند سازنده، همان‌طور که در پنل ثبت شده است (اختیاری)</t>
-  </si>
-  <si>
-    <t>category_code</t>
-  </si>
-  <si>
-    <t>کد یا نام دسته، همان‌طور که در پنل ثبت شده است (الزامی برای کالای تازه، یا یک مقدار برای کل فایل در پنل)</t>
-  </si>
-  <si>
-    <t>vehicle_brand_codes</t>
-  </si>
-  <si>
-    <t>کد یا نام برندهای خودرو، جدا با ویرگول</t>
-  </si>
-  <si>
-    <t>vehicle_models</t>
-  </si>
-  <si>
-    <t>خودروهای سازگار، جدا با ویرگول؛ فقط اضافه می‌شوند و چیزی حذف نمی‌شود</t>
-  </si>
-  <si>
-    <t>part_type</t>
-  </si>
-  <si>
-    <t>GENUINE / OEM / AFTERMARKET (یا: اصلی / او ای ام / افترمارکت)</t>
-  </si>
-  <si>
-    <t>condition</t>
-  </si>
-  <si>
-    <t>NEW / USED / REFURBISHED (یا: نو / کارکرده / بازسازی شده). کالای کارکرده یا بازسازی‌شده بدون عکس واقعی منتشر نمی‌شود.</t>
-  </si>
-  <si>
-    <t>origin</t>
-  </si>
-  <si>
-    <t>DOMESTIC / IMPORTED / UNKNOWN (یا: داخلی / وارداتی / نامشخص)</t>
-  </si>
-  <si>
-    <t>base_currency</t>
-  </si>
-  <si>
-    <t>IRR (ریال) یا AED (درهم). اگر ستون ارز ندارید، واحد ستون قیمت را در پنل انتخاب کنید؛ تومان فقط با انتخاب صریح «تومان، تبدیل به ریال» پذیرفته می‌شود.</t>
-  </si>
-  <si>
-    <t>base_price</t>
-  </si>
-  <si>
-    <t>قیمت پایه در همان ارز؛ ریال عدد صحیح، درهم حداکثر دو رقم اعشار. ارقام فارسی و جداکنندهٔ هزارگان مجازند.</t>
-  </si>
-  <si>
-    <t>on_hand</t>
-  </si>
-  <si>
-    <t>تعداد موجودی. در پنل انتخاب می‌کنید که این عدد جایگزین موجودی فعلی شود (شمارش انبار) یا به آن اضافه شود (کالای رسیده). عدد صحیح.</t>
-  </si>
-  <si>
-    <t>unit</t>
-  </si>
-  <si>
-    <t>واحد فروش (مثل عدد، جفت، دست)</t>
-  </si>
-  <si>
-    <t>low_stock_threshold</t>
-  </si>
-  <si>
-    <t>حد هشدار موجودی (عدد صحیح)</t>
-  </si>
-  <si>
-    <t>override_price_irr</t>
-  </si>
-  <si>
-    <t>قیمت دستی ریالی (اختیاری؛ بر تبدیل خودکار مقدم است)</t>
-  </si>
-  <si>
-    <t>override_price_aed</t>
-  </si>
-  <si>
-    <t>قیمت دستی درهمی برای نمایش/مرجع (اختیاری)</t>
-  </si>
-  <si>
-    <t>description_fa</t>
-  </si>
-  <si>
-    <t>توضیحات و مشخصات فارسی</t>
-  </si>
-  <si>
-    <t>description_en</t>
-  </si>
-  <si>
     <t>is_active</t>
   </si>
   <si>
@@ -300,7 +309,7 @@
     <t>نکته</t>
   </si>
   <si>
-    <t>کالاها را در شیت «کالاها» بنویسید؛ ستون‌هایی را که ندارید خالی بگذارید یا حذف کنید. ترتیب ستون‌ها مهم نیست و در پنل هم می‌توانید ستون‌ها را تطبیق دهید.</t>
+    <t>کالاها را در شیت «کالاها» بنویسید و نمونه‌ها را وارد نکنید. ترتیب ستون‌ها مهم نیست و در پنل هم می‌توانید ستون‌ها را تطبیق دهید.</t>
   </si>
   <si>
     <t>پیش از هر تغییری پیش‌نمایش نشان داده می‌شود؛ تا تأیید نکنید چیزی ثبت نمی‌شود. ردیف خطادار هرگز بی‌صدا حذف نمی‌شود.</t>
@@ -698,21 +707,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="40" customWidth="1"/>
-    <col min="20" max="21" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -736,44 +743,22 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
-      </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: اصلی، او ای ام، افترمارکت" sqref="D2:D5001">
+      <formula1>"اصلی,او ای ام,افترمارکت"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: نو، کارکرده، بازسازی شده" sqref="E2:E5001">
+      <formula1>"نو,کارکرده,بازسازی شده"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: داخلی، وارداتی، نامشخص" sqref="F2:F5001">
+      <formula1>"داخلی,وارداتی,نامشخص"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: ریال، درهم" sqref="G2:G5001">
+      <formula1>"ریال,درهم"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -781,21 +766,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="40" customWidth="1"/>
-    <col min="20" max="21" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -819,174 +802,80 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" t="s">
-        <v>36</v>
-      </c>
-      <c r="T3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>35</v>
-      </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: اصلی، او ای ام، افترمارکت" sqref="D2:D5001">
+      <formula1>"اصلی,او ای ام,افترمارکت"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: نو، کارکرده، بازسازی شده" sqref="E2:E5001">
+      <formula1>"نو,کارکرده,بازسازی شده"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: داخلی، وارداتی، نامشخص" sqref="F2:F5001">
+      <formula1>"داخلی,وارداتی,نامشخص"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: ریال، درهم" sqref="G2:G5001">
+      <formula1>"ریال,درهم"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -994,7 +883,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -1004,16 +893,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1021,13 +910,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1035,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1049,13 +938,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1063,13 +952,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,13 +966,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,13 +980,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,13 +994,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,13 +1008,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,247 +1022,258 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>92</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
         <v>93</v>
       </c>
-      <c r="D22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>94</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
         <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/docs/import/hedax-products-template.xlsx
+++ b/docs/import/hedax-products-template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="112">
   <si>
     <t>کد کالا</t>
   </si>
@@ -42,6 +42,12 @@
     <t>موجودی</t>
   </si>
   <si>
+    <t>واحد</t>
+  </si>
+  <si>
+    <t>کاربرد در خودرو</t>
+  </si>
+  <si>
     <t>00123</t>
   </si>
   <si>
@@ -69,6 +75,12 @@
     <t>4</t>
   </si>
   <si>
+    <t>عدد</t>
+  </si>
+  <si>
+    <t>پژو ۴۰۵، پژو پارس</t>
+  </si>
+  <si>
     <t>TEST-SAMPLE-002</t>
   </si>
   <si>
@@ -96,6 +108,30 @@
     <t>2</t>
   </si>
   <si>
+    <t>دست</t>
+  </si>
+  <si>
+    <t>پژو ۲۰۶، دنا پلاس</t>
+  </si>
+  <si>
+    <t>TEST-SAMPLE-003</t>
+  </si>
+  <si>
+    <t>روغن ترمز (فقط نمونه)</t>
+  </si>
+  <si>
+    <t>950000</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>لیتر</t>
+  </si>
+  <si>
+    <t>سمند، رانا</t>
+  </si>
+  <si>
     <t>عنوان ستون</t>
   </si>
   <si>
@@ -168,7 +204,19 @@
     <t>on_hand</t>
   </si>
   <si>
-    <t>تعداد موجودی. در پنل انتخاب می‌کنید که این عدد جایگزین موجودی فعلی شود (شمارش انبار) یا به آن اضافه شود (کالای رسیده). عدد صحیح.</t>
+    <t>مقدار موجودی به واحد کالا. در پنل انتخاب می‌کنید که این عدد جایگزین موجودی فعلی شود (شمارش انبار) یا به آن اضافه شود (کالای رسیده). برای «عدد» و «دست» فقط عدد صحیح؛ برای «لیتر» با گام ۰٫۵ (مثل ۱۲٫۵).</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>واحد فروش، یکی از واحدهای پنل (محصولات ← واحدها) مثل عدد، دست، لیتر. خالی = «عدد». واحد ناشناخته یا مقدار اعشاری برای واحد بدون اعشار در پیش‌نمایش خطا می‌دهد.</t>
+  </si>
+  <si>
+    <t>vehicle_models</t>
+  </si>
+  <si>
+    <t>کاربرد در خودرو: خودروها جدا با ویرگول (، یا ,)؛ مدل را بعد از نام خودرو بنویسید، مثل «پژو ۲۰۶». نام‌ها با فاصله، نیم‌فاصله، خط تیره یا حروف عربی هم شناخته می‌شوند. خودروی تازه فقط پس از تأیید در پیش‌نمایش ساخته می‌شود و نام خیلی شبیه به خودروی موجود برای اتصال پیشنهاد می‌شود. فقط اضافه می‌شود و چیزی حذف نمی‌شود. عنوان‌های «کاربرد»، «خودرو» و «مدل خودرو» هم شناخته می‌شوند.</t>
   </si>
   <si>
     <t>ستون‌های اختیاری</t>
@@ -225,37 +273,13 @@
     <t>IKCO, SAIPA</t>
   </si>
   <si>
-    <t>خودروهای سازگار</t>
-  </si>
-  <si>
-    <t>vehicle_models</t>
-  </si>
-  <si>
-    <t>خودروهای سازگار، جدا با ویرگول؛ فقط اضافه می‌شوند و چیزی حذف نمی‌شود</t>
-  </si>
-  <si>
-    <t>پژو ۲۰۶، سمند</t>
-  </si>
-  <si>
-    <t>واحد فروش</t>
-  </si>
-  <si>
-    <t>unit</t>
-  </si>
-  <si>
-    <t>واحد فروش (مثل عدد، جفت، دست)</t>
-  </si>
-  <si>
-    <t>عدد</t>
-  </si>
-  <si>
     <t>حد هشدار موجودی</t>
   </si>
   <si>
     <t>low_stock_threshold</t>
   </si>
   <si>
-    <t>حد هشدار موجودی (عدد صحیح)</t>
+    <t>حد هشدار موجودی به واحد کالا (مثل موجودی)</t>
   </si>
   <si>
     <t>1</t>
@@ -707,15 +731,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="9" width="16" customWidth="1"/>
+    <col min="3" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -742,6 +767,12 @@
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -766,15 +797,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="9" width="16" customWidth="1"/>
+    <col min="3" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -802,63 +834,116 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -893,16 +978,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -910,13 +995,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -924,13 +1009,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -938,13 +1023,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -952,13 +1037,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -966,13 +1051,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -980,13 +1065,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -994,13 +1079,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1008,13 +1093,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1022,258 +1107,258 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/docs/import/hedax-products-template.xlsx
+++ b/docs/import/hedax-products-template.xlsx
@@ -13,17 +13,44 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="135">
   <si>
     <t>کد کالا</t>
   </si>
   <si>
+    <t>شماره فنی</t>
+  </si>
+  <si>
     <t>نام قطعه</t>
   </si>
   <si>
+    <t>نام انگلیسی</t>
+  </si>
+  <si>
+    <t>شماره‌های معادل</t>
+  </si>
+  <si>
+    <t>شماره‌های جایگزین</t>
+  </si>
+  <si>
+    <t>برند سازنده</t>
+  </si>
+  <si>
     <t>کد دسته</t>
   </si>
   <si>
+    <t>برند خودرو</t>
+  </si>
+  <si>
+    <t>کاربرد در خودرو</t>
+  </si>
+  <si>
+    <t>مشخصات فنی</t>
+  </si>
+  <si>
+    <t>توضیحات</t>
+  </si>
+  <si>
     <t>نوع قطعه</t>
   </si>
   <si>
@@ -33,6 +60,9 @@
     <t>منشا</t>
   </si>
   <si>
+    <t>واحد</t>
+  </si>
+  <si>
     <t>ارز پایه</t>
   </si>
   <si>
@@ -42,21 +72,30 @@
     <t>موجودی</t>
   </si>
   <si>
-    <t>واحد</t>
-  </si>
-  <si>
-    <t>کاربرد در خودرو</t>
-  </si>
-  <si>
     <t>00123</t>
   </si>
   <si>
+    <t>15208-65F0A</t>
+  </si>
+  <si>
     <t>فیلتر روغن پژو ۴۰۵ (فقط نمونه)</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>W 7008</t>
+  </si>
+  <si>
     <t>FILTER</t>
   </si>
   <si>
+    <t>پژو ۴۰۵، پژو پارس</t>
+  </si>
+  <si>
+    <t>قطر: 76mm؛ ارتفاع: 79mm</t>
+  </si>
+  <si>
     <t>اصلی</t>
   </si>
   <si>
@@ -66,6 +105,9 @@
     <t>داخلی</t>
   </si>
   <si>
+    <t>عدد</t>
+  </si>
+  <si>
     <t>ریال</t>
   </si>
   <si>
@@ -75,12 +117,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>عدد</t>
-  </si>
-  <si>
-    <t>پژو ۴۰۵، پژو پارس</t>
-  </si>
-  <si>
     <t>TEST-SAMPLE-002</t>
   </si>
   <si>
@@ -90,6 +126,9 @@
     <t>BRAKE</t>
   </si>
   <si>
+    <t>پژو ۲۰۶، دنا پلاس</t>
+  </si>
+  <si>
     <t>افترمارکت</t>
   </si>
   <si>
@@ -99,6 +138,9 @@
     <t>وارداتی</t>
   </si>
   <si>
+    <t>دست</t>
+  </si>
+  <si>
     <t>درهم</t>
   </si>
   <si>
@@ -108,28 +150,46 @@
     <t>2</t>
   </si>
   <si>
-    <t>دست</t>
-  </si>
-  <si>
-    <t>پژو ۲۰۶، دنا پلاس</t>
-  </si>
-  <si>
     <t>TEST-SAMPLE-003</t>
   </si>
   <si>
     <t>روغن ترمز (فقط نمونه)</t>
   </si>
   <si>
+    <t>سمند، رانا</t>
+  </si>
+  <si>
+    <t>لیتر</t>
+  </si>
+  <si>
     <t>950000</t>
   </si>
   <si>
     <t>12.5</t>
   </si>
   <si>
-    <t>لیتر</t>
-  </si>
-  <si>
-    <t>سمند، رانا</t>
+    <t>TEST-SAMPLE-004</t>
+  </si>
+  <si>
+    <t>0446533471</t>
+  </si>
+  <si>
+    <t>لنت ترمز جلو بدون قیمت (فقط نمونه)</t>
+  </si>
+  <si>
+    <t>GDB3425</t>
+  </si>
+  <si>
+    <t>04465-33500</t>
+  </si>
+  <si>
+    <t>پژو ۲۰۶ (1390-1400)</t>
+  </si>
+  <si>
+    <t>جنس: سرامیکی</t>
+  </si>
+  <si>
+    <t>بدون قیمت و موجودی: در سایت «درخواست تأمین» نشان داده می‌شود.</t>
   </si>
   <si>
     <t>عنوان ستون</t>
@@ -153,6 +213,12 @@
     <t>0450102805</t>
   </si>
   <si>
+    <t>technical_number</t>
+  </si>
+  <si>
+    <t>شماره فنی (کد قطعه نزد سازنده)؛ متن. به فهرست کدهای فنی کالا اضافه می‌شود و قابل جست‌وجوست. همان شماره با برند دیگر کالای دیگری است.</t>
+  </si>
+  <si>
     <t>name_fa</t>
   </si>
   <si>
@@ -162,12 +228,81 @@
     <t>بلبرینگ چرخ جلو</t>
   </si>
   <si>
+    <t>name_en</t>
+  </si>
+  <si>
+    <t>نام انگلیسی (اختیاری)</t>
+  </si>
+  <si>
+    <t>Front wheel bearing</t>
+  </si>
+  <si>
+    <t>equivalent_numbers</t>
+  </si>
+  <si>
+    <t>شماره‌های معادل: همین قطعه از سازنده‌های دیگر؛ جدا با ویرگول. در جست‌وجوی سایت هم پیدا می‌شوند. فقط اضافه می‌شوند (حذف نمی‌شوند).</t>
+  </si>
+  <si>
+    <t>WK 512, 0 450 905 133</t>
+  </si>
+  <si>
+    <t>replacement_numbers</t>
+  </si>
+  <si>
+    <t>شماره‌هایی که جایگزین این قطعه شده‌اند؛ جدا با ویرگول.</t>
+  </si>
+  <si>
+    <t>0450102806</t>
+  </si>
+  <si>
+    <t>manufacturer_brand</t>
+  </si>
+  <si>
+    <t>نام برند سازنده، همان‌طور که در پنل ثبت شده است (اختیاری)</t>
+  </si>
+  <si>
+    <t>ایساکو</t>
+  </si>
+  <si>
     <t>category_code</t>
   </si>
   <si>
     <t>کد یا نام دسته، همان‌طور که در پنل ثبت شده است (الزامی برای کالای تازه، یا یک مقدار برای کل فایل در پنل)</t>
   </si>
   <si>
+    <t>vehicle_brand_codes</t>
+  </si>
+  <si>
+    <t>کد یا نام برندهای خودرو، جدا با ویرگول</t>
+  </si>
+  <si>
+    <t>IKCO, SAIPA</t>
+  </si>
+  <si>
+    <t>vehicle_models</t>
+  </si>
+  <si>
+    <t>کاربرد در خودرو: خودروها جدا با ویرگول (، یا ,)؛ مدل را بعد از نام خودرو بنویسید، مثل «پژو ۲۰۶». نام‌ها با فاصله، نیم‌فاصله، خط تیره یا حروف عربی هم شناخته می‌شوند. خودروی تازه فقط پس از تأیید در پیش‌نمایش ساخته می‌شود و نام خیلی شبیه به خودروی موجود برای اتصال پیشنهاد می‌شود. فقط اضافه می‌شود و چیزی حذف نمی‌شود. عنوان‌های «کاربرد»، «خودرو» و «مدل خودرو» هم شناخته می‌شوند.</t>
+  </si>
+  <si>
+    <t>specs</t>
+  </si>
+  <si>
+    <t>مشخصات فنی به شکل «عنوان: مقدار» جدا با «؛» (یا هر کدام در یک خط). اگر پر باشد جای مشخصات قبلی قطعه را می‌گیرد.</t>
+  </si>
+  <si>
+    <t>قطر: 80mm؛ طول: 150mm</t>
+  </si>
+  <si>
+    <t>description_fa</t>
+  </si>
+  <si>
+    <t>توضیحات و مشخصات فارسی</t>
+  </si>
+  <si>
+    <t>قطر ۱۵ میلی‌متر، به همراه توپی</t>
+  </si>
+  <si>
     <t>part_type</t>
   </si>
   <si>
@@ -186,6 +321,12 @@
     <t>داخلی / وارداتی / نامشخص (یا DOMESTIC / IMPORTED / UNKNOWN)</t>
   </si>
   <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>واحد فروش، یکی از واحدهای پنل (محصولات ← واحدها) مثل عدد، دست، لیتر. خالی = «عدد». واحد ناشناخته یا مقدار اعشاری برای واحد بدون اعشار در پیش‌نمایش خطا می‌دهد.</t>
+  </si>
+  <si>
     <t>base_currency</t>
   </si>
   <si>
@@ -207,72 +348,12 @@
     <t>مقدار موجودی به واحد کالا. در پنل انتخاب می‌کنید که این عدد جایگزین موجودی فعلی شود (شمارش انبار) یا به آن اضافه شود (کالای رسیده). برای «عدد» و «دست» فقط عدد صحیح؛ برای «لیتر» با گام ۰٫۵ (مثل ۱۲٫۵).</t>
   </si>
   <si>
-    <t>unit</t>
-  </si>
-  <si>
-    <t>واحد فروش، یکی از واحدهای پنل (محصولات ← واحدها) مثل عدد، دست، لیتر. خالی = «عدد». واحد ناشناخته یا مقدار اعشاری برای واحد بدون اعشار در پیش‌نمایش خطا می‌دهد.</t>
-  </si>
-  <si>
-    <t>vehicle_models</t>
-  </si>
-  <si>
-    <t>کاربرد در خودرو: خودروها جدا با ویرگول (، یا ,)؛ مدل را بعد از نام خودرو بنویسید، مثل «پژو ۲۰۶». نام‌ها با فاصله، نیم‌فاصله، خط تیره یا حروف عربی هم شناخته می‌شوند. خودروی تازه فقط پس از تأیید در پیش‌نمایش ساخته می‌شود و نام خیلی شبیه به خودروی موجود برای اتصال پیشنهاد می‌شود. فقط اضافه می‌شود و چیزی حذف نمی‌شود. عنوان‌های «کاربرد»، «خودرو» و «مدل خودرو» هم شناخته می‌شوند.</t>
-  </si>
-  <si>
     <t>ستون‌های اختیاری</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>در صورت نیاز، با همین عنوان به شیت «کالاها» اضافه کنید:</t>
   </si>
   <si>
-    <t>شماره فنی</t>
-  </si>
-  <si>
-    <t>technical_number</t>
-  </si>
-  <si>
-    <t>شماره فنی (کد قطعه نزد سازنده)؛ متن. به فهرست کدهای فنی کالا اضافه می‌شود و قابل جست‌وجوست. همان شماره با برند دیگر کالای دیگری است.</t>
-  </si>
-  <si>
-    <t>نام انگلیسی</t>
-  </si>
-  <si>
-    <t>name_en</t>
-  </si>
-  <si>
-    <t>نام انگلیسی (اختیاری)</t>
-  </si>
-  <si>
-    <t>Front wheel bearing</t>
-  </si>
-  <si>
-    <t>برند سازنده</t>
-  </si>
-  <si>
-    <t>manufacturer_brand</t>
-  </si>
-  <si>
-    <t>نام برند سازنده، همان‌طور که در پنل ثبت شده است (اختیاری)</t>
-  </si>
-  <si>
-    <t>ایساکو</t>
-  </si>
-  <si>
-    <t>برند خودرو</t>
-  </si>
-  <si>
-    <t>vehicle_brand_codes</t>
-  </si>
-  <si>
-    <t>کد یا نام برندهای خودرو، جدا با ویرگول</t>
-  </si>
-  <si>
-    <t>IKCO, SAIPA</t>
-  </si>
-  <si>
     <t>حد هشدار موجودی</t>
   </si>
   <si>
@@ -301,18 +382,6 @@
   </si>
   <si>
     <t>قیمت دستی درهمی برای نمایش/مرجع (اختیاری)</t>
-  </si>
-  <si>
-    <t>توضیحات فارسی</t>
-  </si>
-  <si>
-    <t>description_fa</t>
-  </si>
-  <si>
-    <t>توضیحات و مشخصات فارسی</t>
-  </si>
-  <si>
-    <t>قطر ۱۵ میلی‌متر، به همراه توپی</t>
   </si>
   <si>
     <t>توضیحات انگلیسی</t>
@@ -731,20 +800,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="36" customWidth="1"/>
+    <col min="1" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="16" style="1" customWidth="1"/>
+    <col min="7" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="11" max="19" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -753,10 +825,10 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -774,19 +846,43 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: اصلی، او ای ام، افترمارکت" sqref="D2:D5001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: اصلی، او ای ام، افترمارکت" sqref="M2:M5001">
       <formula1>"اصلی,او ای ام,افترمارکت"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: نو، کارکرده، بازسازی شده" sqref="E2:E5001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: نو، کارکرده، بازسازی شده" sqref="N2:N5001">
       <formula1>"نو,کارکرده,بازسازی شده"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: داخلی، وارداتی، نامشخص" sqref="F2:F5001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: داخلی، وارداتی، نامشخص" sqref="O2:O5001">
       <formula1>"داخلی,وارداتی,نامشخص"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: ریال، درهم" sqref="G2:G5001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: ریال، درهم" sqref="Q2:Q5001">
       <formula1>"ریال,درهم"</formula1>
     </dataValidation>
   </dataValidations>
@@ -797,20 +893,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="36" customWidth="1"/>
+    <col min="1" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="16" style="1" customWidth="1"/>
+    <col min="7" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="11" max="19" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -819,10 +918,10 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -840,124 +939,279 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M5" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="N5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" t="s">
         <v>30</v>
       </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" t="s">
-        <v>38</v>
+      <c r="Q5" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: اصلی، او ای ام، افترمارکت" sqref="D2:D5001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: اصلی، او ای ام، افترمارکت" sqref="M2:M5001">
       <formula1>"اصلی,او ای ام,افترمارکت"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: نو، کارکرده، بازسازی شده" sqref="E2:E5001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: نو، کارکرده، بازسازی شده" sqref="N2:N5001">
       <formula1>"نو,کارکرده,بازسازی شده"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: داخلی، وارداتی، نامشخص" sqref="F2:F5001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: داخلی، وارداتی، نامشخص" sqref="O2:O5001">
       <formula1>"داخلی,وارداتی,نامشخص"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: ریال، درهم" sqref="G2:G5001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="مقدار نامعتبر" error="یکی از این‌ها: ریال، درهم" sqref="Q2:Q5001">
       <formula1>"ریال,درهم"</formula1>
     </dataValidation>
   </dataValidations>
@@ -968,7 +1222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -978,16 +1232,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -995,13 +1249,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1009,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1023,13 +1277,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1037,13 +1291,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1051,13 +1305,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1065,13 +1319,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1079,13 +1333,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1093,13 +1347,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,13 +1361,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1121,13 +1375,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,230 +1389,272 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>105</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>108</v>
+        <v>127</v>
+      </c>
+      <c r="D27" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
